--- a/artfynd/S 42-2022 artfynd.xlsx
+++ b/artfynd/S 42-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105379541</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82321213</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,6 +1067,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82321232</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1180,6 +1200,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82321237</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1308,6 +1333,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82321521</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1437,6 +1467,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024850</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1566,6 +1601,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024890</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1695,6 +1735,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024932</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1824,6 +1869,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024944</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1953,6 +2003,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024971</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2087,6 +2142,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024981</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2216,6 +2276,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024991</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2345,6 +2410,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024998</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2474,6 +2544,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025004</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2603,6 +2678,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025021</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2737,6 +2817,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025030</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2866,6 +2951,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025051</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2995,6 +3085,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025062</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3124,6 +3219,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025077</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3253,6 +3353,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025088</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3382,6 +3487,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025110</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3511,6 +3621,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025123</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3640,6 +3755,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025145</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3769,6 +3889,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025155</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3898,6 +4023,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025194</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4027,6 +4157,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025210</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4156,6 +4291,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025224</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4285,6 +4425,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025240</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4414,6 +4559,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025262</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4543,6 +4693,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025287</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4668,6 +4823,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025304</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4793,6 +4953,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84025315</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4914,6 +5079,11 @@
           <t>Biogeografisk uppföljning av vedlevande evertebrater</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112500444</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5033,6 +5203,11 @@
       <c r="AY35" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av vedlevande evertebrater</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112500446</t>
         </is>
       </c>
     </row>
@@ -5162,6 +5337,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79433343</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5283,6 +5463,11 @@
           <t>Biogeografisk uppföljning av vedlevande evertebrater</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112500447</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5395,6 +5580,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130342994</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5519,6 +5709,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105379369</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5643,6 +5838,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105379396</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5767,8 +5967,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105379413</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>